--- a/hira_material_automation/output/monthly/202601_202607__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-04T22:02:41</t>
+          <t>2026-07-14T22:02:33</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15057dc3e2403615847d35a95d1918ffe032d3c0f4e58bc7b574fccc830abdde</t>
+          <t>23deff7f602e420b0bc6d2285869a23913d39e3cc3c5819749387e8cf6b04daf</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202607__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202607__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14T22:02:33</t>
+          <t>2026-07-24T22:09:27</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23deff7f602e420b0bc6d2285869a23913d39e3cc3c5819749387e8cf6b04daf</t>
+          <t>b202effe3736873d13fc87bdf4beaf0e1863f265a67da78cfbc070c9383940dd</t>
         </is>
       </c>
     </row>
